--- a/dropBD/baking.xlsx
+++ b/dropBD/baking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Drop_Coffe/dropBD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B030E342-824C-D442-A1D1-FAF9FACBF550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B55FD5A-CB50-DA4F-94EF-A540687F79F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="4020" windowWidth="28240" windowHeight="16340" xr2:uid="{90CD58F9-1BC9-314C-A03C-720B7143E2A5}"/>
+    <workbookView xWindow="560" yWindow="500" windowWidth="28240" windowHeight="16280" xr2:uid="{90CD58F9-1BC9-314C-A03C-720B7143E2A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>bakery products</t>
   </si>
@@ -108,13 +108,43 @@
   </si>
   <si>
     <t>Слоёное тесто и щедрая начинка из сулугуни и адыгейского сыра.</t>
+  </si>
+  <si>
+    <t>croissant.png</t>
+  </si>
+  <si>
+    <t>Cinnamon_Bun.png</t>
+  </si>
+  <si>
+    <t>Poppy_Bun_with_Glaze.png</t>
+  </si>
+  <si>
+    <t>Juicy.png</t>
+  </si>
+  <si>
+    <t>Pie.png</t>
+  </si>
+  <si>
+    <t>Triangle_apple.png</t>
+  </si>
+  <si>
+    <t>Triangle_cheese.png</t>
+  </si>
+  <si>
+    <t>Puff_pastry.png</t>
+  </si>
+  <si>
+    <t>Khachapuri.png</t>
+  </si>
+  <si>
+    <t>Monogram.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -124,14 +154,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="15"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Apple Color Emoji"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Apple Color Emoji"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -154,10 +180,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -492,136 +517,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C9144C-0302-1447-93FF-F210B1916BA7}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="71.1640625" customWidth="1"/>
+    <col min="3" max="3" width="185.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>119</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>229</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>89</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>139</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>89</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>159</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>99</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>99</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>139</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>139</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
